--- a/globallbz1_p_ttl_8.xlsx
+++ b/globallbz1_p_ttl_8.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B2" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C2" t="n">
         <v>30000</v>
@@ -687,25 +687,25 @@
         <v>5052</v>
       </c>
       <c r="E2" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="F2" t="n">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="G2" t="n">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="H2" t="n">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="I2" t="n">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="J2" t="n">
-        <v>244</v>
+        <v>113</v>
       </c>
       <c r="K2" t="n">
-        <v>1416.206542346071</v>
+        <v>1424.11333620486</v>
       </c>
       <c r="L2" t="n">
         <v>8</v>
@@ -718,7 +718,7 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>171.5453638279912</t>
+          <t>167.9523929280221</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -727,40 +727,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B3" t="n">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="C3" t="n">
         <v>30000</v>
       </c>
       <c r="D3" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>5052</v>
+      </c>
+      <c r="E3" t="n">
+        <v>147</v>
+      </c>
+      <c r="F3" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>147</v>
+      </c>
+      <c r="H3" t="n">
+        <v>162.7857142857143</v>
+      </c>
+      <c r="I3" t="n">
+        <v>147</v>
+      </c>
+      <c r="J3" t="n">
+        <v>195</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1479.867509086479</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>163.9857348261569</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="C4" t="n">
         <v>30000</v>
@@ -787,10 +809,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B5" t="n">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="C5" t="n">
         <v>30000</v>
@@ -817,10 +839,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B6" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="C6" t="n">
         <v>30000</v>
@@ -847,10 +869,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
         <v>30000</v>
@@ -880,37 +902,59 @@
         <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
         <v>30000</v>
       </c>
       <c r="D8" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+        <v>5052</v>
+      </c>
+      <c r="E8" t="n">
+        <v>198</v>
+      </c>
+      <c r="F8" t="n">
+        <v>214</v>
+      </c>
+      <c r="G8" t="n">
+        <v>198</v>
+      </c>
+      <c r="H8" t="n">
+        <v>214</v>
+      </c>
+      <c r="I8" t="n">
+        <v>198</v>
+      </c>
+      <c r="J8" t="n">
+        <v>223</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1290.31441436713</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>165.83954133545595</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C9" t="n">
         <v>30000</v>
@@ -937,40 +981,62 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="C10" t="n">
         <v>30000</v>
       </c>
       <c r="D10" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>5052</v>
+      </c>
+      <c r="E10" t="n">
+        <v>128</v>
+      </c>
+      <c r="F10" t="n">
+        <v>155.1052631578947</v>
+      </c>
+      <c r="G10" t="n">
+        <v>128</v>
+      </c>
+      <c r="H10" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>128</v>
+      </c>
+      <c r="J10" t="n">
+        <v>155</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1442.356725184032</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>176.05647776490287</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C11" t="n">
         <v>30000</v>
@@ -997,92 +1063,92 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" t="n">
         <v>30000</v>
       </c>
       <c r="D12" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E12" t="n">
-        <v>149</v>
-      </c>
-      <c r="F12" t="n">
-        <v>223</v>
-      </c>
-      <c r="G12" t="n">
-        <v>149</v>
-      </c>
-      <c r="H12" t="n">
-        <v>149</v>
-      </c>
-      <c r="I12" t="n">
-        <v>149</v>
-      </c>
-      <c r="J12" t="n">
-        <v>223</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1383.555956921019</v>
-      </c>
-      <c r="L12" t="n">
-        <v>8</v>
-      </c>
+        <v>5056</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>164.32618469965473</t>
-        </is>
-      </c>
-      <c r="T12" t="n">
-        <v>8</v>
-      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B13" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="C13" t="n">
         <v>30000</v>
       </c>
       <c r="D13" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+        <v>5052</v>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>184</v>
+      </c>
+      <c r="G13" t="n">
+        <v>148</v>
+      </c>
+      <c r="H13" t="n">
+        <v>159</v>
+      </c>
+      <c r="I13" t="n">
+        <v>159</v>
+      </c>
+      <c r="J13" t="n">
+        <v>159</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1603.212763787735</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>171.92514829045572</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B14" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C14" t="n">
         <v>30000</v>
@@ -1109,92 +1175,92 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B15" t="n">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="C15" t="n">
         <v>30000</v>
       </c>
       <c r="D15" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+        <v>5052</v>
+      </c>
+      <c r="E15" t="n">
+        <v>129</v>
+      </c>
+      <c r="F15" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>129</v>
+      </c>
+      <c r="H15" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>129</v>
+      </c>
+      <c r="J15" t="n">
+        <v>219</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1504.683931165174</v>
+      </c>
+      <c r="L15" t="n">
+        <v>8</v>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>162.07891726118976</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C16" t="n">
         <v>30000</v>
       </c>
       <c r="D16" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E16" t="n">
-        <v>112</v>
-      </c>
-      <c r="F16" t="n">
-        <v>226.25</v>
-      </c>
-      <c r="G16" t="n">
-        <v>112</v>
-      </c>
-      <c r="H16" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>112</v>
-      </c>
-      <c r="J16" t="n">
-        <v>212</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1455.761177970195</v>
-      </c>
-      <c r="L16" t="n">
-        <v>8</v>
-      </c>
+        <v>5056</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>162.84386443229494</t>
-        </is>
-      </c>
-      <c r="T16" t="n">
-        <v>8</v>
-      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B17" t="n">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="C17" t="n">
         <v>30000</v>
@@ -1221,7 +1287,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B18" t="n">
         <v>83</v>
@@ -1230,46 +1296,24 @@
         <v>30000</v>
       </c>
       <c r="D18" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E18" t="n">
-        <v>139</v>
-      </c>
-      <c r="F18" t="n">
-        <v>144</v>
-      </c>
-      <c r="G18" t="n">
-        <v>139</v>
-      </c>
-      <c r="H18" t="n">
-        <v>144</v>
-      </c>
-      <c r="I18" t="n">
-        <v>139</v>
-      </c>
-      <c r="J18" t="n">
-        <v>147</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1563.615510895055</v>
-      </c>
-      <c r="L18" t="n">
-        <v>8</v>
-      </c>
+        <v>5056</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>169.72543814250696</t>
-        </is>
-      </c>
-      <c r="T18" t="n">
-        <v>8</v>
-      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/globallbz1_p_ttl_8.xlsx
+++ b/globallbz1_p_ttl_8.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,648 +673,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B2" t="n">
-        <v>79</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E2" t="n">
-        <v>112</v>
-      </c>
-      <c r="F2" t="n">
-        <v>202</v>
-      </c>
-      <c r="G2" t="n">
-        <v>113</v>
-      </c>
-      <c r="H2" t="n">
-        <v>113</v>
-      </c>
-      <c r="I2" t="n">
-        <v>113</v>
-      </c>
-      <c r="J2" t="n">
-        <v>113</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1424.11333620486</v>
-      </c>
-      <c r="L2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>167.9523929280221</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B3" t="n">
-        <v>147</v>
-      </c>
-      <c r="C3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E3" t="n">
-        <v>147</v>
-      </c>
-      <c r="F3" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>147</v>
-      </c>
-      <c r="H3" t="n">
-        <v>162.7857142857143</v>
-      </c>
-      <c r="I3" t="n">
-        <v>147</v>
-      </c>
-      <c r="J3" t="n">
-        <v>195</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1479.867509086479</v>
-      </c>
-      <c r="L3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>163.9857348261569</t>
-        </is>
-      </c>
-      <c r="T3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B4" t="n">
-        <v>126</v>
-      </c>
-      <c r="C4" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B5" t="n">
-        <v>71</v>
-      </c>
-      <c r="C5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>47</v>
-      </c>
-      <c r="B6" t="n">
-        <v>142</v>
-      </c>
-      <c r="C6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B7" t="n">
-        <v>153</v>
-      </c>
-      <c r="C7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B8" t="n">
-        <v>79</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E8" t="n">
-        <v>198</v>
-      </c>
-      <c r="F8" t="n">
-        <v>214</v>
-      </c>
-      <c r="G8" t="n">
-        <v>198</v>
-      </c>
-      <c r="H8" t="n">
-        <v>214</v>
-      </c>
-      <c r="I8" t="n">
-        <v>198</v>
-      </c>
-      <c r="J8" t="n">
-        <v>223</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1290.31441436713</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>165.83954133545595</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>38</v>
-      </c>
-      <c r="B9" t="n">
-        <v>104</v>
-      </c>
-      <c r="C9" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>30</v>
-      </c>
-      <c r="B10" t="n">
-        <v>81</v>
-      </c>
-      <c r="C10" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E10" t="n">
-        <v>128</v>
-      </c>
-      <c r="F10" t="n">
-        <v>155.1052631578947</v>
-      </c>
-      <c r="G10" t="n">
-        <v>128</v>
-      </c>
-      <c r="H10" t="n">
-        <v>129.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>128</v>
-      </c>
-      <c r="J10" t="n">
-        <v>155</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1442.356725184032</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>176.05647776490287</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>38</v>
-      </c>
-      <c r="B11" t="n">
-        <v>107</v>
-      </c>
-      <c r="C11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>34</v>
-      </c>
-      <c r="B12" t="n">
-        <v>87</v>
-      </c>
-      <c r="C12" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>49</v>
-      </c>
-      <c r="B13" t="n">
-        <v>149</v>
-      </c>
-      <c r="C13" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E13" t="n">
-        <v>148</v>
-      </c>
-      <c r="F13" t="n">
-        <v>184</v>
-      </c>
-      <c r="G13" t="n">
-        <v>148</v>
-      </c>
-      <c r="H13" t="n">
-        <v>159</v>
-      </c>
-      <c r="I13" t="n">
-        <v>159</v>
-      </c>
-      <c r="J13" t="n">
-        <v>159</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1603.212763787735</v>
-      </c>
-      <c r="L13" t="n">
-        <v>8</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>171.92514829045572</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>37</v>
-      </c>
-      <c r="B14" t="n">
-        <v>106</v>
-      </c>
-      <c r="C14" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>32</v>
-      </c>
-      <c r="B15" t="n">
-        <v>78</v>
-      </c>
-      <c r="C15" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5052</v>
-      </c>
-      <c r="E15" t="n">
-        <v>129</v>
-      </c>
-      <c r="F15" t="n">
-        <v>222.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>129</v>
-      </c>
-      <c r="H15" t="n">
-        <v>129.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>129</v>
-      </c>
-      <c r="J15" t="n">
-        <v>219</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1504.683931165174</v>
-      </c>
-      <c r="L15" t="n">
-        <v>8</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>162.07891726118976</t>
-        </is>
-      </c>
-      <c r="T15" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>42</v>
-      </c>
-      <c r="B16" t="n">
-        <v>121</v>
-      </c>
-      <c r="C16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D16" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>34</v>
-      </c>
-      <c r="B17" t="n">
-        <v>83</v>
-      </c>
-      <c r="C17" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>34</v>
-      </c>
-      <c r="B18" t="n">
-        <v>83</v>
-      </c>
-      <c r="C18" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5056</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
